--- a/data/trans_orig/IQ2606_R2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ2606_R2-Clase-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>44555</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>37371</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>52138</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,31%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>43,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,21%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>52900</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>45188</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>60476</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>45445</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>59913</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>61,05%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>52,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>44555</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>37057</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>52126</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>52,31%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86707</t>
+          <t>87706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>108806</t>
+          <t>107942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,82%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40619</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33036</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47803</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,69%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>56,12%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33746</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>26170</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>41458</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>26733</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>41201</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>38,95%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>30,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>47,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>40619</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>33048</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48117</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>47,69%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>63014</t>
+          <t>63878</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>85113</t>
+          <t>84114</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85174</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85174</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85174</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>86646</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>86646</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>86646</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85174</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85174</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85174</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1065,72 +1065,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>64848</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57698</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>71498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>69,47%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>62798</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54821</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>70126</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>55206</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>69774</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>68,77%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>76,8%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>64848</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>57500</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>71627</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>69,47%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>61,6%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116775</t>
+          <t>117244</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>137324</t>
+          <t>137371</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,39%</t>
         </is>
       </c>
     </row>
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28500</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>21850</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>35650</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>23,41%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>28517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21189</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>36494</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>21541</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>36109</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>31,23%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>23,2%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>28500</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>21721</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35848</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>30,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>38,4%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>47338</t>
+          <t>47291</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67887</t>
+          <t>67418</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>93348</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>93348</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>93348</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>91315</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>91315</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>91315</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>135</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>93348</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>93348</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>93348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>51454</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>44048</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>58743</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>62,11%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>70,91%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>77</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>52526</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>44370</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>59190</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45642</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>59876</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>62,98%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>70,97%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>51454</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>43973</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58223</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>62,11%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>53,08%</t>
+          <t>54,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93264</t>
+          <t>93651</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113210</t>
+          <t>113877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,5%</t>
         </is>
       </c>
     </row>
@@ -1526,67 +1526,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>31389</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24100</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38795</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>37,89%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29,09%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>46,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>30872</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24208</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>39028</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>23522</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>37756</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>37,02%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>31389</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>24620</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>38870</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>37,89%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53031</t>
+          <t>52364</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>72977</t>
+          <t>72590</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>82843</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>82843</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>82843</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>83398</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>83398</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>83398</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>82843</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>82843</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>82843</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>120416</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>107176</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>132256</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>54,96%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>48,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>60,37%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>124807</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>112909</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>134904</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>113678</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>135565</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>62,63%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>56,66%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>67,7%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>120416</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>108153</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>132743</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>54,96%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,59%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>227702</t>
+          <t>229893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260331</t>
+          <t>262380</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,72%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98664</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>86824</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>111904</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>45,04%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>39,63%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>51,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74460</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>64363</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>86358</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>63702</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>85589</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>37,37%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>32,3%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>43,34%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>140</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98664</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>86337</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>110927</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>45,04%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>158016</t>
+          <t>155967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190645</t>
+          <t>188454</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>219080</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>219080</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>219080</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>289</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>199267</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>199267</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>199267</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>219080</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>219080</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>219080</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2094,72 +2094,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>72459</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>63138</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>83476</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>52,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>45,53%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>60,19%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>81886</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>71123</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>92031</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>72075</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>91726</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>56,77%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>49,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>72459</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>62914</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>83242</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>52,25%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>49,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>63,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>139514</t>
+          <t>141212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168971</t>
+          <t>168555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -2207,72 +2207,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66221</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55204</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75542</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>39,81%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>54,47%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>62343</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>52198</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>73106</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>52503</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>72154</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>43,23%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>50,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>66221</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>55438</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75766</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>47,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>36,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113939</t>
+          <t>114355</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>143396</t>
+          <t>141698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,09%</t>
         </is>
       </c>
     </row>
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>138680</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>138680</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>138680</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>144229</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>144229</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>144229</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>138680</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>138680</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>138680</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2437,72 +2437,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>38318</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>30837</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>44702</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>54,17%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>43,59%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>63,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>31015</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>24626</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>36842</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>24954</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>36937</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>59,63%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>47,35%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>70,84%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>38318</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>31873</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>45048</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>54,17%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>63,68%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>59463</t>
+          <t>60497</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>77817</t>
+          <t>78216</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,72%</t>
         </is>
       </c>
     </row>
@@ -2550,72 +2550,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32424</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>26040</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>39905</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>45,83%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>36,81%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>56,41%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>20993</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15166</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>27382</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>15071</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>27054</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>40,37%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>29,16%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>32424</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>25694</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>38869</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>45,83%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>52,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44934</t>
+          <t>44535</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>63288</t>
+          <t>62254</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>70742</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>70742</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>70742</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>52008</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>52008</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>52008</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>70742</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>70742</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>70742</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2780,72 +2780,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>392050</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>370024</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>412673</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>56,83%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>53,64%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>59,82%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>592</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>405932</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>385387</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>426032</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>384375</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>425291</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>61,8%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>58,67%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>392050</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>369518</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>414526</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>770095</t>
+          <t>768513</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>828197</t>
+          <t>828175</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2893,72 +2893,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>297818</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>277195</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>319844</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>43,17%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>40,18%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>46,36%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>356</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>250932</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>230832</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>271477</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>231573</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>272489</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>38,2%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>297818</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>275342</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>320350</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>43,17%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>46,44%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>518535</t>
+          <t>518557</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>576637</t>
+          <t>578219</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,93%</t>
         </is>
       </c>
     </row>
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>985</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>689868</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>689868</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>689868</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>948</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>656864</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>656864</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>656864</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>985</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>689868</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>689868</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>689868</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3189,7 +3189,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3357,72 +3357,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>81507</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>74496</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>86944</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,67%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>89,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>67892</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>62248</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>72788</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>61757</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>72106</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>81507</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>74913</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>86636</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140519</t>
+          <t>141800</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>156611</t>
+          <t>157088</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,68%</t>
         </is>
       </c>
     </row>
@@ -3470,72 +3470,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15658</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10221</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22669</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12081</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7185</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>17725</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18216</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>15,11%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>8,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,16%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15658</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>10529</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22252</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,11%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20527</t>
+          <t>20050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36619</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -3583,57 +3583,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>97165</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>97165</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>97165</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>79973</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>79973</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>79973</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>97165</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>97165</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>97165</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3700,72 +3700,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>84732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>77840</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>91947</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>76,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69,87%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>82,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>80466</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>72945</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>87214</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>72669</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>86874</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>77,94%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>70,66%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>84,48%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>84732</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>76376</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>91323</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>76,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153493</t>
+          <t>155150</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>174621</t>
+          <t>175515</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>71,51%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,35%</t>
+          <t>81,77%</t>
         </is>
       </c>
     </row>
@@ -3813,72 +3813,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26673</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>19458</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33565</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>23,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,13%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22771</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>16023</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>30292</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>16363</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>30568</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>22,06%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>29,34%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>26673</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>20082</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>35029</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>23,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40021</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>59492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -3926,57 +3926,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111405</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111405</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111405</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103237</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103237</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103237</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111405</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111405</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111405</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4043,72 +4043,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>54097</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48049</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59824</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>73,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>64,85%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>80,74%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>39456</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>33212</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>44866</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>33052</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45288</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>63,8%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>72,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>54097</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>46682</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>60329</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>73,01%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84157</t>
+          <t>83606</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101772</t>
+          <t>100887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -4156,72 +4156,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>20001</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>14274</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>26049</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>26,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>19,26%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>35,15%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>22384</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16974</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>28628</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>16552</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>28788</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,2%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>46,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>20001</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>13769</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>27416</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>26,99%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34166</t>
+          <t>35051</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51781</t>
+          <t>52332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,5%</t>
         </is>
       </c>
     </row>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>74098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>74098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>61840</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>74098</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>74098</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>74098</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4386,72 +4386,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>147193</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>135929</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>158258</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>70,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>65,05%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>75,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>159872</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>148262</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>170592</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>148415</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>170247</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>72,64%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,36%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>77,51%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>147193</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>135489</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>157950</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>292370</t>
+          <t>290496</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>322285</t>
+          <t>322585</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -4499,72 +4499,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>61766</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>50701</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>73030</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>29,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>24,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>34,95%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>60231</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>49511</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>71841</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>49856</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>71688</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>27,36%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>22,49%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,64%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>61766</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>51009</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>73470</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>29,56%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>106777</t>
+          <t>106477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136692</t>
+          <t>138566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -4612,57 +4612,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>208959</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>208959</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>208959</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>335</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>220103</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>220103</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>220103</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>208959</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>208959</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>208959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4729,72 +4729,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>98380</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>88548</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>107027</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,23%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>62,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,32%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>87494</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>77878</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>95509</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>77849</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>96303</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>64,8%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>70,73%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>98380</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>89229</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>107839</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>69,23%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>171881</t>
+          <t>173157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>198137</t>
+          <t>198716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,71%</t>
         </is>
       </c>
     </row>
@@ -4842,72 +4842,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>43723</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>35076</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>53555</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>30,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>24,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>47532</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>39517</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>57148</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>38723</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>57177</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,2%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>43723</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>34264</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>52874</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>78992</t>
+          <t>78413</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>105248</t>
+          <t>103972</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -4955,57 +4955,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>142103</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>142103</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>142103</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>204</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>135026</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>135026</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>135026</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>142103</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>142103</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>142103</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5072,72 +5072,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>46689</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>40403</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>52716</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>68,84%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>59,57%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>77,72%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>45081</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>38840</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>49948</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>38294</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>50276</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>74,53%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>64,21%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>82,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>46689</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>39798</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>52208</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>68,84%</t>
-        </is>
-      </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,68%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>82517</t>
+          <t>82666</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>100248</t>
+          <t>100601</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,4%</t>
         </is>
       </c>
     </row>
@@ -5185,72 +5185,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>21136</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>15109</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>27422</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>31,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>22,28%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>40,43%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>15410</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>10543</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>21651</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>10215</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>22197</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>25,47%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>35,79%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>21136</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>15617</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>28027</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>31,16%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28067</t>
+          <t>27714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45798</t>
+          <t>45649</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,58%</t>
         </is>
       </c>
     </row>
@@ -5298,57 +5298,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>67825</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>60491</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>60491</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>60491</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>67825</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5415,72 +5415,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>512597</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>492215</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>530431</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>73,07%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>70,16%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>75,61%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>729</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>480262</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>458042</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>496747</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>460880</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>500048</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>72,69%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>69,33%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>512597</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>491719</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>530240</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>73,07%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>965794</t>
+          <t>964827</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1018869</t>
+          <t>1019000</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,8%</t>
         </is>
       </c>
     </row>
@@ -5533,67 +5533,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>188957</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>171123</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>209339</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>26,93%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>29,84%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>180408</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>163923</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>202628</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>160622</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>199790</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>27,31%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>24,81%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>30,67%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>188957</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>171314</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>209835</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>26,93%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>343356</t>
+          <t>343225</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>396431</t>
+          <t>397398</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -5641,57 +5641,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>1005</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>701554</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>701554</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>701554</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>995</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>660670</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>660670</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>660670</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>1005</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>701554</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>701554</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>701554</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5824,7 +5824,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5992,72 +5992,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>29425</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>25131</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>33200</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>79,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>68,32%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>90,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25182</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>20712</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27865</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>83,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,87%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>92,65%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29583</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24053</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>27961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6067,32 +6067,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54765</t>
+          <t>54511</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>48046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59702</t>
+          <t>59299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,63%</t>
         </is>
       </c>
     </row>
@@ -6105,72 +6105,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7361</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3586</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11655</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>20,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4893</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2210</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9363</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>16,27%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7,35%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>31,13%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8089</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4412</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13619</t>
+          <t>8992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6180,32 +6180,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>12398</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>7610</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19337</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,19%</t>
         </is>
       </c>
     </row>
@@ -6223,17 +6223,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>36786</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>36786</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30075</t>
+          <t>36786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6258,17 +6258,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>37672</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37672</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37672</t>
+          <t>30123</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6293,17 +6293,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>66909</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>66909</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>67748</t>
+          <t>66909</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6335,72 +6335,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>18635</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14999</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19910</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>75,34%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>20035</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>16007</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>22366</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>82,26%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>65,72%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>17025</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6410,32 +6410,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>39207</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35955</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42891</t>
+          <t>41852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,46%</t>
         </is>
       </c>
     </row>
@@ -6448,72 +6448,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4911</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>6,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>24,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4321</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>17,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>34,28%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1343</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>7847</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6523,32 +6523,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5664</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2713</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>9649</t>
+          <t>10153</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -6561,57 +6561,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19910</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19910</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>19910</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>24356</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>24356</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>24356</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>24872</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>45604</t>
+          <t>44782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6678,72 +6678,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14956</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12105</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16233</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>92,13%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>74,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8566</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4790</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10532</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>74,11%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>41,44%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>16447</t>
+          <t>8658</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13608</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>90,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6753,32 +6753,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25014</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19246</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27333</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>84,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -6791,72 +6791,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4128</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>7,87%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>25,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2993</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1027</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6769</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>25,89%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>58,56%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1221</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4060</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>53,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6866,32 +6866,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4213</t>
+          <t>4468</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1894</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>31,46%</t>
         </is>
       </c>
     </row>
@@ -6904,57 +6904,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16233</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16233</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16233</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>11559</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11559</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>11559</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6979,17 +6979,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29227</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7021,72 +7021,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>39724</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>35795</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>41523</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>93,76%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>98,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>33000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>28747</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35704</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>87,91%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>76,58%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>95,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>43586</t>
+          <t>31158</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39363</t>
+          <t>26765</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45584</t>
+          <t>33692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7096,32 +7096,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>76586</t>
+          <t>70881</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71466</t>
+          <t>65927</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>80262</t>
+          <t>74412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,85%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -7134,72 +7134,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2644</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6573</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>4537</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8790</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>12,09%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7209,32 +7209,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7664</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -7247,57 +7247,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>42368</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>42368</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>42368</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>37537</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>37537</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>37537</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46713</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>46713</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46713</t>
+          <t>35651</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7322,17 +7322,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>84250</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>84250</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84250</t>
+          <t>78019</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7364,72 +7364,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>31457</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26664</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>35244</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>79,65%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>20347</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>17293</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>22080</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>87,76%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>33709</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28143</t>
+          <t>13961</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>18837</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7439,32 +7439,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>54056</t>
+          <t>48395</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>48125</t>
+          <t>42109</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>58703</t>
+          <t>52322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>88,03%</t>
         </is>
       </c>
     </row>
@@ -7477,72 +7477,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>8037</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>4250</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>12830</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>20,35%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>10,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>32,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2838</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1105</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5892</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>12,24%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>25,41%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8193</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>5980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7552,32 +7552,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16962</t>
+          <t>17326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>29,15%</t>
         </is>
       </c>
     </row>
@@ -7590,57 +7590,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39494</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39494</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39494</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>23185</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23185</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23185</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41902</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7665,17 +7665,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>65087</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>65087</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>65087</t>
+          <t>59435</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7707,72 +7707,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18050</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14369</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>19895</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>86,71%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>69,03%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9990</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>6222</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>12035</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>76,74%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>47,8%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>92,45%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>20551</t>
+          <t>10316</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>6172</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22794</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>45,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>30541</t>
+          <t>28367</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26181</t>
+          <t>23204</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33964</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,5%</t>
         </is>
       </c>
     </row>
@@ -7825,32 +7825,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3028</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>921</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>6447</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7860,32 +7860,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2994</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>862</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>7256</t>
+          <t>7485</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>24,46%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7895,32 +7895,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6022</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2599</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>10382</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -7933,57 +7933,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>20816</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>20816</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>20816</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>13018</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>13018</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>13018</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8008,17 +8008,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8050,72 +8050,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>152247</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>143135</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>158809</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>86,7%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>81,51%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>90,43%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>117121</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>108928</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>124039</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>77,96%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>163781</t>
+          <t>112727</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155402</t>
+          <t>104790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>171480</t>
+          <t>119475</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>280902</t>
+          <t>264973</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>269262</t>
+          <t>252200</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>291090</t>
+          <t>274743</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -8163,72 +8163,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>23361</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>16799</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>32473</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>13,3%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>9,57%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>18,49%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>22611</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>15693</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>30804</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>22,04%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24967</t>
+          <t>23365</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17268</t>
+          <t>16617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>33346</t>
+          <t>31302</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8238,32 +8238,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>47578</t>
+          <t>46726</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>37390</t>
+          <t>36956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>59218</t>
+          <t>59499</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>19,09%</t>
         </is>
       </c>
     </row>
@@ -8276,57 +8276,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>175608</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>175608</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>175608</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>139732</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>139732</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>139732</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>188748</t>
+          <t>136092</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>188748</t>
+          <t>136092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>188748</t>
+          <t>136092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8351,17 +8351,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>328480</t>
+          <t>311699</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>328480</t>
+          <t>311699</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>328480</t>
+          <t>311699</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
